--- a/templates/07-business-cases-template.xlsx
+++ b/templates/07-business-cases-template.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Blank template" sheetId="2" r:id="rId2"/>
+    <sheet name="Blank template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -448,114 +447,6 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.7  Business Cases</t>
-        </is>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valuation and decision</t>
-        </is>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What it is for</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assembles the justification for a change: the need, the options considered, the recommended option and what it is expected to be worth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when a decision-maker has to approve funding and needs the need, the options and the value in one place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confused with</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The business case is the container; financial analysis is one of its contents. An item that turns on how the return was calculated is financial analysis, while one that turns on whether the recommendation was justified at all is the business case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tasks</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.4 Define Change Strategy  ·  6.2 Define Future State  ·  7.6 Analyze Potential Value and Recommend Solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knowledge areas</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6, 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The blank template is on the next sheet — fill it in.</t>
-        </is>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A10:B10"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
